--- a/ONCHO/Entomological survey Survey/Nigeria/2024/ng_oncho_2501_3_flies_sort_all.xlsx
+++ b/ONCHO/Entomological survey Survey/Nigeria/2024/ng_oncho_2501_3_flies_sort_all.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\yumbad\Repositories\dsa-forms\ONCHO\Entomological survey Survey\Nigeria\2024\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{96E6504E-5151-4BB1-88A9-93C31A04CC55}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5E9FD2BE-5236-4A09-975E-1DE7B4E6CBEE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21240" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="survey" sheetId="1" r:id="rId1"/>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3514" uniqueCount="938">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3514" uniqueCount="937">
   <si>
     <t>type</t>
   </si>
@@ -2833,9 +2833,6 @@
   </si>
   <si>
     <t>You entered there were zero flies, if that isn't the case, please update your previous answers accordingly.</t>
-  </si>
-  <si>
-    <t>. != No</t>
   </si>
   <si>
     <t>. != 'No'</t>
@@ -3931,7 +3928,7 @@
         <v>928</v>
       </c>
       <c r="B16" s="25" t="s">
-        <v>935</v>
+        <v>934</v>
       </c>
       <c r="C16" s="26" t="s">
         <v>930</v>
@@ -3939,13 +3936,13 @@
       <c r="D16" s="27"/>
       <c r="E16" s="26"/>
       <c r="F16" s="26" t="s">
-        <v>933</v>
+        <v>932</v>
       </c>
       <c r="G16" s="26" t="s">
         <v>931</v>
       </c>
       <c r="H16" s="26" t="s">
-        <v>934</v>
+        <v>933</v>
       </c>
       <c r="I16" s="26"/>
       <c r="J16" s="27" t="s">
@@ -4054,7 +4051,7 @@
         <v>929</v>
       </c>
       <c r="C20" s="26" t="s">
-        <v>936</v>
+        <v>935</v>
       </c>
       <c r="D20" s="27"/>
       <c r="E20" s="26"/>
@@ -4065,7 +4062,7 @@
         <v>931</v>
       </c>
       <c r="H20" s="26" t="s">
-        <v>937</v>
+        <v>936</v>
       </c>
       <c r="I20" s="26"/>
       <c r="J20" s="27" t="s">
